--- a/docs/MindX 6.0.RC1 通信矩阵.xlsx
+++ b/docs/MindX 6.0.RC1 通信矩阵.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" tabRatio="530"/>
+    <workbookView windowHeight="17655" tabRatio="530"/>
   </bookViews>
   <sheets>
     <sheet name="MindX SDK" sheetId="9" r:id="rId1"/>
@@ -450,7 +450,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="47">
   <si>
     <t>源设备</t>
   </si>
@@ -568,6 +568,9 @@
   </si>
   <si>
     <t>用户平面</t>
+  </si>
+  <si>
+    <t>配置的master节点所在服务器</t>
   </si>
   <si>
     <t>用户指定（默认9000）</t>
@@ -1322,7 +1325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1340,9 +1343,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1837,22 +1837,22 @@
       <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1884,22 +1884,22 @@
       <c r="I3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1931,22 +1931,22 @@
       <c r="I4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1978,22 +1978,22 @@
       <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2011,36 +2011,36 @@
         <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2049,10 +2049,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>30</v>
@@ -2067,27 +2067,27 @@
         <v>19</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2102,39 +2102,39 @@
         <v>18</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="7">
+        <v>42</v>
+      </c>
+      <c r="F8" s="6">
         <v>53</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>43</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="8" t="s">
         <v>26</v>
       </c>
     </row>
